--- a/proposal/15_Requirements_Traceability_Matrix.xlsx
+++ b/proposal/15_Requirements_Traceability_Matrix.xlsx
@@ -133,7 +133,7 @@
     <t xml:space="preserve">Answer management questions in plain language based only on the loaded document set</t>
   </si>
   <si>
-    <t xml:space="preserve">Grounded generation with citations; independent grounding check; refusal when unsupported; Arabic and English (s.9.2 steps 5-6)</t>
+    <t xml:space="preserve">Grounded generation with citations; independent grounding check; refusal when unsupported; multilingual (s.9.2 steps 5-6)</t>
   </si>
   <si>
     <t xml:space="preserve">Intelligence service, model gateway, web app</t>
@@ -175,7 +175,7 @@
     <t xml:space="preserve">Three categories: investors; partners/counterparties; customers/members; GCC-specific pipeline</t>
   </si>
   <si>
-    <t xml:space="preserve">Category-typed relationships; configurable pipelines and stage sets per category; GCC template (s.2.2, s.8.3)</t>
+    <t xml:space="preserve">Category-typed relationships; configurable pipelines and stage sets per category; GCC template for market entry (s.2.2, s.8.3)</t>
   </si>
   <si>
     <t xml:space="preserve">Core API, CRM schema, web app</t>
@@ -340,10 +340,10 @@
     <t xml:space="preserve">N1</t>
   </si>
   <si>
-    <t xml:space="preserve">Arabic and English documents, questions, answers and interface (assumed; Document 13 gap 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OCR with Arabic; multilingual embeddings; RTL layout; per-language evaluation</t>
+    <t xml:space="preserve">Documents, questions, answers and interface in the languages the corpus actually uses; English primary (mix to be confirmed; Document 13 gap 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCR configured per language; multilingual embeddings; localisable interface with RTL available if later needed; per-language evaluation</t>
   </si>
   <si>
     <t xml:space="preserve">Intelligence service, web app</t>
@@ -355,7 +355,7 @@
     <t xml:space="preserve">s.6 Answer faithfulness</t>
   </si>
   <si>
-    <t xml:space="preserve">Arabic golden-set scores within 10 points of English</t>
+    <t xml:space="preserve">Every in-scope language within 10 points of English on the golden set</t>
   </si>
   <si>
     <t xml:space="preserve">3.2 step 5</t>
@@ -1032,7 +1032,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>49</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
         <v>105</v>
       </c>
